--- a/Listing/DJM01N.xlsx
+++ b/Listing/DJM01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="435">
   <si>
     <t/>
   </si>
@@ -112,13 +112,25 @@
     <t>10</t>
   </si>
   <si>
+    <t>20141502</t>
+  </si>
+  <si>
+    <t>DUNHILL MIXTURES 12S</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
     <t>20137298</t>
   </si>
   <si>
     <t>L.STRIKE BRY FRZ 20S</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>20102468</t>
@@ -127,7 +139,7 @@
     <t>LUCKY/S PRPLE BOST20</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>10010112</t>
@@ -136,7 +148,7 @@
     <t>LUCKY STRIKE FILTR20</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>10010113</t>
@@ -145,7 +157,7 @@
     <t>LUCKY.ST CL.SWITC 20</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>20098080</t>
@@ -280,9 +292,6 @@
     <t>MAGNUM KRT CKLT 12'S</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
     <t>20134964</t>
   </si>
   <si>
@@ -541,12 +550,6 @@
     <t>FORTE MNTHL BKS 20'S</t>
   </si>
   <si>
-    <t>20132551</t>
-  </si>
-  <si>
-    <t>FORTE VANILA BKS 20S</t>
-  </si>
-  <si>
     <t>20132549</t>
   </si>
   <si>
@@ -613,9 +616,6 @@
     <t>DJRM CGRILLOS FC 12S</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>10010081</t>
   </si>
   <si>
@@ -748,12 +748,6 @@
     <t>TEREA OASIS PRL 20'S</t>
   </si>
   <si>
-    <t>20128087</t>
-  </si>
-  <si>
-    <t>TEREA PRPL WAVE 20S</t>
-  </si>
-  <si>
     <t>20132739</t>
   </si>
   <si>
@@ -802,12 +796,6 @@
     <t>TEREA BLACK RUBY20S</t>
   </si>
   <si>
-    <t>20138225</t>
-  </si>
-  <si>
-    <t>TEREA BLACK PURPLE20</t>
-  </si>
-  <si>
     <t>20139349</t>
   </si>
   <si>
@@ -1102,6 +1090,12 @@
     <t>WIN KRT NANGKA 12'S</t>
   </si>
   <si>
+    <t>20108797</t>
+  </si>
+  <si>
+    <t>WIN BOLD 20'S</t>
+  </si>
+  <si>
     <t>20135739</t>
   </si>
   <si>
@@ -1178,12 +1172,6 @@
   </si>
   <si>
     <t>JUARA  JAMBU12S</t>
-  </si>
-  <si>
-    <t>20108797</t>
-  </si>
-  <si>
-    <t>WIN BOLD 20'S</t>
   </si>
   <si>
     <t>20085760</t>
@@ -1720,7 +1708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F210"/>
+  <dimension ref="A1:F208"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1967,15 +1955,15 @@
         <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1984,7 +1972,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1992,10 +1980,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -2004,7 +1992,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -2012,10 +2000,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -2024,7 +2012,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -2032,19 +2020,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -2052,10 +2040,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -2064,7 +2052,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -2072,10 +2060,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -2084,18 +2072,18 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -2104,18 +2092,18 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -2124,18 +2112,18 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -2144,18 +2132,18 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -2164,7 +2152,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -2172,10 +2160,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -2184,7 +2172,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -2192,10 +2180,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -2204,7 +2192,7 @@
         <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -2212,10 +2200,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -2224,7 +2212,7 @@
         <v>8</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -2232,10 +2220,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -2244,7 +2232,7 @@
         <v>8</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2252,10 +2240,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -2264,7 +2252,7 @@
         <v>8</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -2272,10 +2260,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -2284,18 +2272,18 @@
         <v>8</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -2304,38 +2292,38 @@
         <v>8</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -2344,7 +2332,7 @@
         <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -2352,10 +2340,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -2364,18 +2352,18 @@
         <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -2384,18 +2372,18 @@
         <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -2404,7 +2392,7 @@
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2412,10 +2400,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2424,7 +2412,7 @@
         <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2432,10 +2420,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2444,18 +2432,18 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2464,18 +2452,18 @@
         <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2484,7 +2472,7 @@
         <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2492,10 +2480,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2504,18 +2492,18 @@
         <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2524,18 +2512,18 @@
         <v>11</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2544,18 +2532,18 @@
         <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2564,18 +2552,18 @@
         <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2584,7 +2572,7 @@
         <v>11</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2592,30 +2580,30 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2624,18 +2612,18 @@
         <v>14</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2644,7 +2632,7 @@
         <v>14</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2652,10 +2640,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2664,7 +2652,7 @@
         <v>14</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2672,10 +2660,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2684,7 +2672,7 @@
         <v>14</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2692,10 +2680,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2704,7 +2692,7 @@
         <v>14</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2712,10 +2700,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2724,7 +2712,7 @@
         <v>14</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2732,10 +2720,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2744,7 +2732,7 @@
         <v>14</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2752,10 +2740,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2764,7 +2752,7 @@
         <v>14</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2772,10 +2760,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2784,18 +2772,18 @@
         <v>14</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2804,18 +2792,18 @@
         <v>14</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2824,7 +2812,7 @@
         <v>14</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2832,10 +2820,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2844,7 +2832,7 @@
         <v>14</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2852,10 +2840,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2864,7 +2852,7 @@
         <v>14</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2872,19 +2860,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2892,10 +2880,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2904,18 +2892,18 @@
         <v>17</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2924,18 +2912,18 @@
         <v>17</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2944,7 +2932,7 @@
         <v>17</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2952,10 +2940,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2964,7 +2952,7 @@
         <v>17</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2972,10 +2960,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2984,7 +2972,7 @@
         <v>17</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2992,10 +2980,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -3004,7 +2992,7 @@
         <v>17</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3012,10 +3000,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -3024,7 +3012,7 @@
         <v>17</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3032,10 +3020,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -3044,7 +3032,7 @@
         <v>17</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3052,10 +3040,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -3064,18 +3052,18 @@
         <v>17</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -3084,18 +3072,18 @@
         <v>17</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -3104,7 +3092,7 @@
         <v>17</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3112,19 +3100,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3132,10 +3120,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -3144,7 +3132,7 @@
         <v>20</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3152,10 +3140,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -3164,7 +3152,7 @@
         <v>20</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3172,10 +3160,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -3184,7 +3172,7 @@
         <v>20</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3192,10 +3180,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -3204,7 +3192,7 @@
         <v>20</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3212,10 +3200,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -3224,7 +3212,7 @@
         <v>20</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3232,10 +3220,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -3244,7 +3232,7 @@
         <v>20</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3252,10 +3240,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -3264,7 +3252,7 @@
         <v>20</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3272,19 +3260,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3292,10 +3280,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -3304,7 +3292,7 @@
         <v>23</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3312,10 +3300,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -3324,7 +3312,7 @@
         <v>23</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3332,10 +3320,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -3352,10 +3340,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -3372,10 +3360,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -3392,10 +3380,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -3412,10 +3400,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -3432,10 +3420,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3452,10 +3440,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3472,10 +3460,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3492,10 +3480,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3504,7 +3492,7 @@
         <v>23</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3512,10 +3500,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3524,7 +3512,7 @@
         <v>23</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3532,10 +3520,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3544,7 +3532,7 @@
         <v>23</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3687,7 +3675,7 @@
         <v>23</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3867,7 +3855,7 @@
         <v>23</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4047,7 +4035,7 @@
         <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4067,7 +4055,7 @@
         <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4084,7 +4072,7 @@
         <v>32</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4147,7 +4135,7 @@
         <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4164,10 +4152,10 @@
         <v>32</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4184,10 +4172,10 @@
         <v>32</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4224,7 +4212,7 @@
         <v>32</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4244,7 +4232,7 @@
         <v>32</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4307,7 +4295,7 @@
         <v>17</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4324,7 +4312,7 @@
         <v>32</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4344,10 +4332,10 @@
         <v>32</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4387,7 +4375,7 @@
         <v>20</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4407,7 +4395,7 @@
         <v>20</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4427,7 +4415,7 @@
         <v>20</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4447,7 +4435,7 @@
         <v>20</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4467,7 +4455,7 @@
         <v>20</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4604,10 +4592,10 @@
         <v>32</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4624,10 +4612,10 @@
         <v>32</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4647,7 +4635,7 @@
         <v>23</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4667,7 +4655,7 @@
         <v>23</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4687,7 +4675,7 @@
         <v>23</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4707,7 +4695,7 @@
         <v>23</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4784,7 +4772,7 @@
         <v>32</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4801,10 +4789,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4821,10 +4809,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4844,7 +4832,7 @@
         <v>35</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4864,7 +4852,7 @@
         <v>35</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4884,7 +4872,7 @@
         <v>35</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4904,7 +4892,7 @@
         <v>35</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4924,7 +4912,7 @@
         <v>35</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4944,7 +4932,7 @@
         <v>35</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4964,7 +4952,7 @@
         <v>35</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4984,7 +4972,7 @@
         <v>35</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5004,7 +4992,7 @@
         <v>35</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5024,10 +5012,10 @@
         <v>35</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5044,7 +5032,7 @@
         <v>35</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5061,13 +5049,13 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -5081,10 +5069,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5101,10 +5089,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5121,10 +5109,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5141,10 +5129,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5161,10 +5149,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5181,10 +5169,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5201,10 +5189,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5221,10 +5209,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5241,10 +5229,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5261,10 +5249,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5281,10 +5269,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5301,10 +5289,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5321,10 +5309,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5341,10 +5329,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5361,10 +5349,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5381,10 +5369,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5401,10 +5389,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5421,10 +5409,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5441,10 +5429,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5461,10 +5449,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5481,10 +5469,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5501,10 +5489,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5521,10 +5509,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5541,10 +5529,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5561,13 +5549,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5581,13 +5569,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -5601,13 +5589,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -5621,13 +5609,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5641,13 +5629,13 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5661,13 +5649,13 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5681,13 +5669,13 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5701,13 +5689,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -5721,13 +5709,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5741,13 +5729,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -5761,13 +5749,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -5781,13 +5769,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -5801,13 +5789,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -5821,13 +5809,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -5841,13 +5829,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -5861,13 +5849,13 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -5881,53 +5869,13 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F209" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A210" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F210" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
